--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02E142C-0565-0646-87DF-90AD831FBCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B965E68F-15CD-F546-9A0B-BB1B1CEBB7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="173">
   <si>
     <t>BAU Expected Capacity Factors</t>
   </si>
@@ -605,6 +605,15 @@
   <si>
     <t>https://nucleus.iaea.org/sites/INPRO/df1/Session%202/19-Suprawoto.pdf</t>
   </si>
+  <si>
+    <t>Sidik Permana, Nuri Trianti, and Adi Rahmansyah</t>
+  </si>
+  <si>
+    <t>Nuclear energy contribution potential to secure electricity demand with low carbon emission and low risk of power plant in Indonesia</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/753/1/012048/pdf</t>
+  </si>
 </sst>
 </file>
 
@@ -1141,6 +1150,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1199,9 +1211,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1224,16 +1233,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1256,7 +1265,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9944100" y="3632200"/>
+          <a:off x="10756900" y="3644900"/>
           <a:ext cx="9029700" cy="2171700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1517,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1031"/>
+  <dimension ref="A1:I1035"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="8.6640625" customWidth="1"/>
@@ -1537,16 +1546,16 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1730,7 +1739,7 @@
     </row>
     <row r="36" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="104">
+      <c r="B36" s="78">
         <v>2010</v>
       </c>
     </row>
@@ -1752,154 +1761,174 @@
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="B40" s="65"/>
+      <c r="B40" s="74" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="78">
+        <v>2020</v>
+      </c>
     </row>
     <row r="42" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2"/>
+      <c r="B42" s="65" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2"/>
+      <c r="B43" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2"/>
+      <c r="B44" s="65"/>
+    </row>
+    <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="81" t="s">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="82"/>
-      <c r="H43" s="82"/>
-      <c r="I43" s="82"/>
-    </row>
-    <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="82"/>
-      <c r="C44" s="82"/>
-      <c r="D44" s="82"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="82"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-    </row>
-    <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="82"/>
-      <c r="C45" s="82"/>
-      <c r="D45" s="82"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="82"/>
-      <c r="I45" s="82"/>
-    </row>
-    <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="82"/>
-      <c r="C46" s="82"/>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-    </row>
-    <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="82"/>
-      <c r="C47" s="82"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
     </row>
     <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="82"/>
-      <c r="C48" s="82"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="82"/>
-      <c r="F48" s="82"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
     </row>
     <row r="49" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="82"/>
-      <c r="C49" s="82"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="82"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="82"/>
-      <c r="I49" s="82"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="83"/>
     </row>
     <row r="50" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="82"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="83"/>
     </row>
     <row r="51" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="82"/>
-      <c r="C51" s="82"/>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
-      <c r="I51" s="82"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
     </row>
     <row r="52" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="82"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
     </row>
     <row r="53" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="82"/>
-      <c r="C53" s="82"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82"/>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82"/>
-      <c r="I53" s="82"/>
+      <c r="B53" s="83"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
     </row>
     <row r="54" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="82"/>
-      <c r="C54" s="82"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
     </row>
     <row r="55" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="82"/>
-      <c r="C55" s="82"/>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-    </row>
-    <row r="56" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+    </row>
+    <row r="56" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="83"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="83"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+    </row>
+    <row r="57" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="83"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="83"/>
+    </row>
+    <row r="58" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="83"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="83"/>
+    </row>
+    <row r="59" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="83"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="83"/>
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="83"/>
+    </row>
     <row r="60" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="61" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="62" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2872,10 +2901,14 @@
     <row r="1029" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1030" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1031" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1032" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1033" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1034" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1035" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B43:I55"/>
+    <mergeCell ref="B47:I59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2885,6 +2918,7 @@
     <hyperlink ref="B28" r:id="rId5" xr:uid="{E32369E6-517E-DC43-B8DF-80DC041DCD36}"/>
     <hyperlink ref="B33" r:id="rId6" xr:uid="{31D3C805-F505-AB40-AC7F-7C2BE018D12B}"/>
     <hyperlink ref="B38" r:id="rId7" xr:uid="{B56265E6-1266-1644-8311-402A1FC2CD58}"/>
+    <hyperlink ref="B43" r:id="rId8" xr:uid="{ED1268E7-0774-8647-BC1C-DC9C87DB471F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2905,11 +2939,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2920,14 +2954,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="96" t="s">
+      <c r="B3" s="85"/>
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="84"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -2998,14 +3032,14 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="98" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="84"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="12" t="s">
         <v>25</v>
       </c>
@@ -3087,12 +3121,12 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="87"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="98" t="s">
+      <c r="A5" s="88"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="84"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="12">
         <v>3</v>
       </c>
@@ -3171,14 +3205,14 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="84"/>
-      <c r="C6" s="98" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="84"/>
+      <c r="D6" s="85"/>
       <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
@@ -3257,14 +3291,14 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="98" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="12" t="s">
         <v>28</v>
       </c>
@@ -3343,12 +3377,12 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="87"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="98" t="s">
+      <c r="A8" s="88"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="84"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -3427,14 +3461,14 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="86"/>
-      <c r="C9" s="98" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="84"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="12" t="s">
         <v>32</v>
       </c>
@@ -3513,12 +3547,12 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="98" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="84"/>
+      <c r="D10" s="85"/>
       <c r="E10" s="12" t="s">
         <v>28</v>
       </c>
@@ -3597,12 +3631,12 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="98" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="84"/>
+      <c r="D11" s="85"/>
       <c r="E11" s="12" t="s">
         <v>28</v>
       </c>
@@ -3681,12 +3715,12 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="98" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="84"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="12" t="s">
         <v>28</v>
       </c>
@@ -3731,14 +3765,14 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="98" t="s">
+      <c r="B13" s="87"/>
+      <c r="C13" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="84"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="12" t="s">
         <v>37</v>
       </c>
@@ -3816,12 +3850,12 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="87"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="98" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="84"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="12">
         <v>3</v>
       </c>
@@ -4060,14 +4094,14 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="98" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="84"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
@@ -4107,12 +4141,12 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="87"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="98" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="84"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="12">
         <v>1</v>
       </c>
@@ -4155,14 +4189,14 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="98" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="84"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="12" t="s">
         <v>37</v>
       </c>
@@ -4215,12 +4249,12 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="90"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="98" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="84"/>
+      <c r="D20" s="85"/>
       <c r="E20" s="12" t="s">
         <v>37</v>
       </c>
@@ -4279,12 +4313,12 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="87"/>
-      <c r="B21" s="88"/>
-      <c r="C21" s="98" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="84"/>
+      <c r="D21" s="85"/>
       <c r="E21" s="12">
         <v>2</v>
       </c>
@@ -4343,14 +4377,14 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93" t="s">
+      <c r="A22" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="98" t="s">
+      <c r="B22" s="85"/>
+      <c r="C22" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="84"/>
+      <c r="D22" s="85"/>
       <c r="E22" s="12">
         <v>2</v>
       </c>
@@ -4375,14 +4409,14 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="98" t="s">
+      <c r="B23" s="87"/>
+      <c r="C23" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="84"/>
+      <c r="D23" s="85"/>
       <c r="E23" s="12" t="s">
         <v>28</v>
       </c>
@@ -4407,12 +4441,12 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="90"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="99" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="84"/>
+      <c r="D24" s="85"/>
       <c r="E24" s="12">
         <v>3</v>
       </c>
@@ -4470,12 +4504,12 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="90"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="99" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="84"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="12">
         <v>3</v>
       </c>
@@ -4503,12 +4537,12 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="99" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="84"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="12">
         <v>3</v>
       </c>
@@ -4536,12 +4570,12 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="87"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="98" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="84"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="12">
         <v>3</v>
       </c>
@@ -4712,12 +4746,12 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="100" t="s">
+      <c r="F35" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27" t="s">
@@ -5417,12 +5451,12 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="101" t="s">
+      <c r="A53" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="79"/>
-      <c r="C53" s="79"/>
-      <c r="D53" s="80"/>
+      <c r="B53" s="80"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="81"/>
       <c r="E53" s="26" t="s">
         <v>10</v>
       </c>
@@ -5432,11 +5466,11 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="100" t="s">
+      <c r="F54" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
     </row>
     <row r="55" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27" t="s">
@@ -6224,12 +6258,12 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="102" t="s">
+      <c r="A70" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="80"/>
+      <c r="B70" s="80"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="81"/>
       <c r="E70" s="26" t="s">
         <v>10</v>
       </c>
@@ -7759,11 +7793,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
@@ -7774,14 +7808,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="96" t="s">
+      <c r="B3" s="85"/>
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="84"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -7817,14 +7851,14 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="93" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="84"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
@@ -7869,12 +7903,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="98" t="s">
+      <c r="A5" s="91"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="84"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="12" t="s">
         <v>28</v>
       </c>
@@ -7919,12 +7953,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="87"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="98" t="s">
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="84"/>
+      <c r="D6" s="85"/>
       <c r="E6" s="12">
         <v>1</v>
       </c>
@@ -7969,14 +8003,14 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="84"/>
-      <c r="C7" s="103" t="s">
+      <c r="B7" s="85"/>
+      <c r="C7" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="84"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="12">
         <v>1</v>
       </c>
@@ -8021,14 +8055,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="103" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="84"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -8073,12 +8107,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="103" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="84"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="12">
         <v>1</v>
       </c>
@@ -8123,12 +8157,12 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="98" t="s">
+      <c r="A10" s="88"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="84"/>
+      <c r="D10" s="85"/>
       <c r="E10" s="12">
         <v>1</v>
       </c>
@@ -8184,14 +8218,14 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="89" t="s">
+      <c r="A11" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="103" t="s">
+      <c r="B11" s="87"/>
+      <c r="C11" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="84"/>
+      <c r="D11" s="85"/>
       <c r="E11" s="12">
         <v>1</v>
       </c>
@@ -8236,12 +8270,12 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="103" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="84"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="12">
         <v>1</v>
       </c>
@@ -8286,12 +8320,12 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="103" t="s">
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="84"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="12">
         <v>1</v>
       </c>
@@ -8336,12 +8370,12 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="87"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="103" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="84"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="12">
         <v>1</v>
       </c>
@@ -8478,25 +8512,25 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="84"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="87"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="103" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="84"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="12">
         <v>2</v>
       </c>
@@ -8505,14 +8539,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="103" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="84"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="12">
         <v>1</v>
       </c>
@@ -8530,12 +8564,12 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="87"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="98" t="s">
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="84"/>
+      <c r="D20" s="85"/>
       <c r="E20" s="12">
         <v>1</v>
       </c>
@@ -8556,14 +8590,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="86"/>
-      <c r="C21" s="98" t="s">
+      <c r="B21" s="87"/>
+      <c r="C21" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="84"/>
+      <c r="D21" s="85"/>
       <c r="E21" s="12" t="s">
         <v>28</v>
       </c>
@@ -8584,8 +8618,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="87"/>
-      <c r="B22" s="88"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8610,14 +8644,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="98" t="s">
+      <c r="B23" s="85"/>
+      <c r="C23" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="84"/>
+      <c r="D23" s="85"/>
       <c r="E23" s="12">
         <v>1</v>
       </c>
@@ -8638,14 +8672,14 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="98" t="s">
+      <c r="B24" s="87"/>
+      <c r="C24" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="84"/>
+      <c r="D24" s="85"/>
       <c r="E24" s="12">
         <v>1</v>
       </c>
@@ -8666,12 +8700,12 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="90"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="103" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="84"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="12">
         <v>2</v>
       </c>
@@ -8692,12 +8726,12 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="99" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="84"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="12">
         <v>2</v>
       </c>
@@ -8718,12 +8752,12 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="90"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="99" t="s">
+      <c r="A27" s="91"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="84"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="12">
         <v>2</v>
       </c>
@@ -8744,12 +8778,12 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="98" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="84"/>
+      <c r="D28" s="85"/>
       <c r="E28" s="12">
         <v>2</v>
       </c>
@@ -18811,7 +18845,7 @@
         <v>128</v>
       </c>
       <c r="B4">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -19313,131 +19347,131 @@
       </c>
       <c r="B4" s="64">
         <f>'Capacity Factor-Reports'!B4</f>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="C4" s="64">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="D4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="E4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="J4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="K4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="L4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="M4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="N4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="O4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="P4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Q4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="R4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="S4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="T4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="U4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="V4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="W4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="X4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Y4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Z4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AB4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AC4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AD4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AE4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AF4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AG4" s="64">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25763,131 +25797,131 @@
       </c>
       <c r="B4" s="63">
         <f>'BECF-pre-ret'!B4</f>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="C4" s="63">
         <f>$B$4</f>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="D4" s="63">
         <f t="shared" ref="D4:AG4" si="2">$B$4</f>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="E4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="F4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="H4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="J4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="K4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="L4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="M4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="N4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="O4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="P4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Q4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="R4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="S4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="T4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="U4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="V4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="W4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="X4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Y4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="Z4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AB4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AC4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AD4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AE4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AF4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="AG4" s="63">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
